--- a/dist/SUBMISSION_FINAL/P8_SIDS_JED/p8_sids_worlddevelopment_replication_data.xlsx
+++ b/dist/SUBMISSION_FINAL/P8_SIDS_JED/p8_sids_worlddevelopment_replication_data.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Regression_Coefficients" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Turning_Points" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Robustness" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Figures_Embedded" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +49,25 @@
     <font>
       <b val="1"/>
       <i val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00305496"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -80,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -91,6 +111,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -165,6 +191,61 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="3981450"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="2257425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -590,7 +671,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1357,7 +1437,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1418,7 +1497,6 @@
       <c r="F4" t="n">
         <v>0.252297</v>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1530,7 +1608,6 @@
       <c r="F8" t="n">
         <v>0.242332</v>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1613,7 +1690,6 @@
       <c r="F11" t="n">
         <v>0.264856</v>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1638,7 +1714,6 @@
       <c r="F12" t="n">
         <v>0.508325</v>
       </c>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1663,7 +1738,6 @@
       <c r="F13" t="n">
         <v>0.229871</v>
       </c>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1746,7 +1820,6 @@
       <c r="F16" t="n">
         <v>0.252012</v>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1771,7 +1844,6 @@
       <c r="F17" t="n">
         <v>0.435011</v>
       </c>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1796,7 +1868,6 @@
       <c r="F18" t="n">
         <v>0.495116</v>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1821,7 +1892,6 @@
       <c r="F19" t="n">
         <v>0.402328</v>
       </c>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1846,7 +1916,6 @@
       <c r="F20" t="n">
         <v>0.37826</v>
       </c>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2386,4 +2455,79 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>P8_SIDS_JED — Embedded Figures (data-driven, source-traceable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Each figure below was rendered from a CSV / data file produced by the paper's Stata or R replication pipeline. Provenance is listed under each figure. See 'STATA_REPLICATION_GUIDE.md' (Vietnamese + English) for end-to-end reproduction instructions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Figure 1: figure_1_conceptual_model.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Provenance: scripts/render_conceptual_models.py → matplotlib (theoretical diagram, not data-driven)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Figure 2: figure_2_fip_curve.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Provenance: p8/replication/figures/ ← p8/replication/p8_predicted_curve.csv (R 01_p8_run_models_R.R)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A37:H37"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>